--- a/Raspisanie_Bez_Paralleley.xlsx
+++ b/Raspisanie_Bez_Paralleley.xlsx
@@ -524,14 +524,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>РАСПИСАНИЕ ОСЕНЬ — БЕЗ ПАРАЛЛЕЛЕЙ ТРЕНЕРОВ • 60 мин слот • per-time алгоритм</t>
+          <t>РАСПИСАНИЕ ОСЕНЬ 2 поля 7×7 везде — 60 мин/игра (2×25+5+5, для 2020: 2×20+5+15) — БЕЗ ПАРАЛЛЕЛЕЙ ТРЕНЕРОВ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5*5 на 4*4 помечены жёлтым — это запасные поля. Тренер не может быть в двух местах одновременно — проверка 0 конфликтов.</t>
+          <t>26.08 17:30-20:30 2×7×7+3×5×5 • 27.08 10-13 2×7×7+2×5×5+3×4×4 • далее все даты 2×7×7 — 5×5 на 4×4 жёлтым • тренер не может быть в двух местах одновременно</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -2801,43 +2801,47 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Якимов</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2863,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2869,28 +2873,28 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2916,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2928,22 +2932,22 @@
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
@@ -2965,42 +2969,38 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Группа A</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
@@ -3017,43 +3017,47 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Группа A</t>
+        </is>
+      </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
@@ -3070,43 +3074,47 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Цыганов</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3136,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -3138,28 +3146,28 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -3181,64 +3189,60 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>Группа A</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -3254,128 +3258,136 @@
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные 2</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Группа A</t>
+        </is>
+      </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Женя</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Лысиков</t>
         </is>
       </c>
     </row>
@@ -3397,42 +3409,38 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Красные опасные 2</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3457,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -3470,22 +3478,22 @@
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные 3</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Галимуллин</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3510,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -3517,28 +3525,28 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Агарков</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
@@ -3555,43 +3563,47 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
     </row>
@@ -3608,12 +3620,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -3628,22 +3640,22 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Группа B</t>
+          <t>Группа C</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Куликов</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -3665,7 +3677,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3696,7 +3708,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные 2</t>
+          <t>Красные опасные 3</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -3718,7 +3730,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3733,7 +3745,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
@@ -3749,7 +3761,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Киты 42/11</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -3771,7 +3783,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3786,13 +3798,13 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -3802,12 +3814,12 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3836,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3849,12 +3861,12 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -3871,75 +3883,79 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные 3</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Уразаков</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Лысиков</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3949,50 +3965,50 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Красные опасные 2</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -4002,191 +4018,195 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Киты 42/11</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Якимов</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Крепыши 3</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Седин</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Куликов</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4223,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4224,22 +4244,22 @@
       <c r="G71" s="4" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Красные опасные 3</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -4256,47 +4276,43 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Шкреба</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Якимов</t>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4329,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4328,28 +4344,28 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Крепыши</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
@@ -4366,43 +4382,47 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>Киты 42/11</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Уразаков</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Гурин</t>
         </is>
       </c>
     </row>
@@ -4419,12 +4439,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -4434,28 +4454,28 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Крепыши 3</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -4472,228 +4492,228 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>Майоров</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Поле 7*7 #1</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>7*7</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Куликов</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>Уразаков</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Куликов</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="K76" s="6" t="inlineStr">
-        <is>
-          <t>Лысиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #1</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Профики 2</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>Крепыши 3</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #2</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Акулы 42/11</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Щадин</t>
-        </is>
-      </c>
-      <c r="J78" s="8" t="inlineStr">
-        <is>
-          <t>Спутник-1</t>
-        </is>
-      </c>
-      <c r="K78" s="9" t="inlineStr">
-        <is>
-          <t>Агарков</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #3</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Тетерин</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -4703,50 +4723,50 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Киты 42/11</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Шкреба</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -4756,85 +4776,81 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Уразаков</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Лысиков</t>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4867,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Поле 4*4 #1</t>
+          <t>Поле 4*4 #2</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -4866,28 +4882,28 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Профики 2</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>Крепыши</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4920,12 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Поле 4*4 #2</t>
+          <t>Поле 4*4 #3</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -4919,79 +4935,79 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Тетерин</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #3</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Майоров</t>
-        </is>
-      </c>
-      <c r="J85" s="8" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K85" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
@@ -5010,12 +5026,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -5025,138 +5041,134 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Цыганов</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Шкреба</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #2</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>Шкреба</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="K87" s="6" t="inlineStr">
-        <is>
-          <t>Женя</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>Якимов</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="K88" s="6" t="inlineStr">
-        <is>
-          <t>Седин</t>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Спутник-1</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5185,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Поле 4*4 #1</t>
+          <t>Поле 4*4 #3</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -5188,314 +5200,310 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="8" t="inlineStr">
         <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Майоров</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Школа 16</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Смолкин</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Комета</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Женя</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="I92" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J89" s="8" t="inlineStr">
+      <c r="J92" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K92" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I93" s="9" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
       </c>
-      <c r="J90" s="8" t="inlineStr">
+      <c r="J93" s="8" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K93" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>Тетерин</t>
         </is>
       </c>
-      <c r="J91" s="8" t="inlineStr">
+      <c r="J94" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K91" s="9" t="inlineStr">
+      <c r="K94" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #1</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>Колюжный</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="K92" s="6" t="inlineStr">
-        <is>
-          <t>Майоров</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #2</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>68 школа</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>Шкреба</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>Спутник-1</t>
-        </is>
-      </c>
-      <c r="K93" s="6" t="inlineStr">
-        <is>
-          <t>Агарков</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Гурин</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="K94" s="6" t="inlineStr">
-        <is>
-          <t>Куликов</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -5510,45 +5518,45 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>Крепыши 2</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Колюжный</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>Профики 2</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5563,28 +5571,28 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Шкреба</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5614,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -5622,22 +5630,22 @@
       <c r="G97" s="4" t="inlineStr"/>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Крепыши 2</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Профики 2</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -5659,42 +5667,38 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5715,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -5726,28 +5730,28 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Агарков</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Галимуллин</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5773,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -5785,22 +5789,22 @@
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5826,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -5838,22 +5842,22 @@
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -5875,42 +5879,38 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Агарков</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Шкреба</t>
         </is>
       </c>
     </row>
@@ -14324,16 +14324,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Сводка спортдиректора — без параллелей</t>
+          <t>Сводка спортдиректора — 2×7×7 везде, 60 мин, без параллелей</t>
         </is>
       </c>
     </row>
@@ -14354,351 +14356,568 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Конфликтов: 0</t>
+          <t>Конфликтов (реальных параллелей): 0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>По датам:</t>
+          <t>Слотов всего: 394 (136×7×7 +177×5×5 +81×4×4) — последовательных тайм-слотов 68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26.08</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>15</v>
+          <t>Регламент: 2×25+5 перерыв между таймами +5 между матчами =60 мин; 2020: 2×20+5+15=60 мин</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27.08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>21</v>
+          <t>По датам (факт/ёмкость):</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03.10</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>12</v>
+          <t>26.08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15 / 15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>заполнено 100%</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04.10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>12</v>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>21 / 21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>заполнено 100%</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>12</v>
+          <t>03.10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15 / 15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>заполнено 100%</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>18</v>
+          <t>04.10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15 / 15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>заполнено 100%</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17.10</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>11</v>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11 / 15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>заполнено 73%</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18.10</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9</v>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15 / 21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>заполнено 71%</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24.10</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>9</v>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9 / 15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25.10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>15</v>
+          <t>18.10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9 / 15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31.10</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>12</v>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9 / 15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.11</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>20</v>
+          <t>25.10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15 / 21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>заполнено 71%</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>12</v>
+          <t>31.10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12 / 20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>12</v>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20 / 28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>заполнено 71%</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28.11</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>30</v>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12 / 20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05.12</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>12</v>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12 / 20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12.12</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>13</v>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30 / 42</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>заполнено 71%</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19.12</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>6</v>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12 / 20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>заполнено 60%</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13 / 28</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>заполнено 46%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6 / 20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>заполнено 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Осталось (перенести на весну):</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4 / 28</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>заполнено 14%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа C Орлы 4-Орлы 5</t>
+          <t>Осталось 44 — 80% с тренером Анисимов (19 команд) — нужно 4 доп. даты или вторые тренеры:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A 68 школа-Орлы 2</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа C Орлы 4-Орлы 5 (Анисимов/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Орлы 2-Школа 64/92</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A 68 школа-Орлы 2 (Шкреба/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Школа 16-Орлы 2</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Орлы 2-Школа 64/92 (Анисимов/Тетерин)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа B КС 26-Орлы 3</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Школа 16-Орлы 2 (Смолкин/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Школа 35-Орлы 2</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа B КС 26-Орлы 3 (Кузьмичев/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга  Школа 35-Красные опасные 3</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Школа 35-Орлы 2 (Колюжный/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга  Школа 35-Красные опасные 2</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга  Школа 35-Красные опасные 3 (Колюжный/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга  Красные опасные 3-Школа 35</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга  Школа 35-Красные опасные 2 (Колюжный/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Орлы 2-Комета</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга  Красные опасные 3-Школа 35 (Анисимов/Колюжный)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа B Орлы 3-Молот</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа A Орлы 2-Комета (Анисимов/Женя)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2016-2017 Высшая 5×5 — группы 5×4 Группа A Молот-Огонь 2</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа B Орлы 3-Молот (Анисимов/Цыганов)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2016-2017 Высшая 5×5 — группы 5×4 Группа D Огонь 5-Комета</t>
+          <t>2016-2017 Высшая 5×5 — группы 5×4 Группа A Молот-Огонь 2 (Цыганов/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга  Красные опасные-Молот</t>
+          <t>2016-2017 Высшая 5×5 — группы 5×4 Группа D Огонь 5-Комета (Анисимов/Женя)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга  Комета-Красные опасные</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга  Красные опасные-Молот (Анисимов/Цыганов)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга  Молот-Красные опасные</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга  Комета-Красные опасные (Женя/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга  Красные опасные-Комета</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга  Молот-Красные опасные (Цыганов/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг  школа 76-Крепыши 2</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга  Красные опасные-Комета (Анисимов/Женя)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг  Молот (153/157)-Крепыши</t>
+          <t>2020-2021 Предварительный 13 — 1 круг  школа 76-Крепыши 2 (Глинин/Анисимов)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг  ЯнгФорс-Крепыши 2</t>
+          <t>2020-2021 Предварительный 13 — 1 круг  Молот (153/157)-Крепыши (Вукалов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  ЯнгФорс-Крепыши 2 (Сусляев/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши 2-Барселона (Анисимов/Ботов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши 2-Молот (153/157) (Анисимов/Вукалов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши 3-школа 76 (Анисимов/Глинин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши-школа 76 (Анисимов/Глинин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши 3-ЯнгФорс (Анисимов/Сусляев)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Крепыши-ЯнгФорс (Анисимов/Сусляев)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Барселона-Крепыши 3 (Ботов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Молот (153/157)-Крепыши 3 (Вукалов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг  Барселона-Крепыши (Ботов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2014-2015 Высшая 7×7 — группы 3×6 Группа B Школа 175/96-Орлы 3 (Лысиков/Анисимов)</t>
         </is>
       </c>
     </row>

--- a/Raspisanie_Bez_Paralleley.xlsx
+++ b/Raspisanie_Bez_Paralleley.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet name="Расписание_без_параллелей" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Только_2020_4x4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Расписание_без_параллелей'!$A$4:$K$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Только_2020_4x4'!$A$4:$K$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +63,11 @@
     <font>
       <b val="1"/>
       <color rgb="0016A34A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -109,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -140,6 +147,8 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,14 +533,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>РАСПИСАНИЕ ОСЕНЬ 2 поля 7×7 везде — 60 мин/игра (2×25+5+5, для 2020: 2×20+5+15) — БЕЗ ПАРАЛЛЕЛЕЙ ТРЕНЕРОВ</t>
+          <t>РАСПИСАНИЕ ТОЛЬКО НА ЭТИ 19 ДАТ (без января) — 2 поля 7×7 везде — 60 мин/игра — БЕЗ ПАРАЛЛЕЛЕЙ ТРЕНЕРОВ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26.08 17:30-20:30 2×7×7+3×5×5 • 27.08 10-13 2×7×7+2×5×5+3×4×4 • далее все даты 2×7×7 — 5×5 на 4×4 жёлтым • тренер не может быть в двух местах одновременно</t>
+          <t>2020-2021 — формат 4×4 (отмечено) , может играть на 5×5 поле — жёлтым • 5×5↔4×4 взаимозаменяемы • 26.08 17:30-20:30 2×7×7+3×5×5 • 27.08 10-13 2×7×7+2×5×5+3×4×4 • продолжение в январе — даты пока неизвестны</t>
         </is>
       </c>
     </row>
@@ -646,53 +655,53 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>26.08</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Вт</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -1143,53 +1152,53 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>26.08</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Вт</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -1416,53 +1425,53 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -1799,53 +1808,53 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -2292,53 +2301,53 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -3991,53 +4000,53 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>04.10</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -4427,53 +4436,53 @@
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>10.10</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I75" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J75" s="8" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="K75" s="6" t="inlineStr">
+      <c r="K75" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -4643,106 +4652,106 @@
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>10.10</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>10.10</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K80" s="6" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -4802,53 +4811,53 @@
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J82" s="8" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -5067,53 +5076,53 @@
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J87" s="8" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="K87" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -5332,53 +5341,53 @@
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="G92" s="4" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J92" s="8" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K92" s="9" t="inlineStr">
+      <c r="K92" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -5597,53 +5606,53 @@
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I97" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J97" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K97" s="6" t="inlineStr">
+      <c r="K97" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -5703,53 +5712,53 @@
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="I99" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="J99" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K99" s="6" t="inlineStr">
+      <c r="K99" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -6021,53 +6030,53 @@
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I105" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J105" s="5" t="inlineStr">
+      <c r="J105" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K105" s="6" t="inlineStr">
+      <c r="K105" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -6710,106 +6719,106 @@
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr">
+      <c r="I118" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="K118" s="6" t="inlineStr">
+      <c r="K118" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G119" s="4" t="inlineStr"/>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="G119" s="7" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I119" s="6" t="inlineStr">
+      <c r="I119" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="J119" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K119" s="6" t="inlineStr">
+      <c r="K119" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -6869,106 +6878,106 @@
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="G121" s="7" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="I121" s="6" t="inlineStr">
+      <c r="I121" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J121" s="5" t="inlineStr">
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K121" s="6" t="inlineStr">
+      <c r="K121" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>24.10</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G122" s="4" t="inlineStr"/>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I122" s="6" t="inlineStr">
+      <c r="I122" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J122" s="5" t="inlineStr">
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K122" s="6" t="inlineStr">
+      <c r="K122" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -7028,53 +7037,53 @@
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
+      <c r="I124" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J124" s="8" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K124" s="9" t="inlineStr">
+      <c r="K124" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -7346,53 +7355,53 @@
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G130" s="7" t="inlineStr"/>
-      <c r="H130" s="8" t="inlineStr">
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I130" s="9" t="inlineStr">
+      <c r="I130" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J130" s="8" t="inlineStr">
+      <c r="J130" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
+      <c r="K130" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -7611,53 +7620,53 @@
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr">
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I135" s="9" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J135" s="8" t="inlineStr">
+      <c r="J135" s="5" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K135" s="9" t="inlineStr">
+      <c r="K135" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -8035,53 +8044,53 @@
       </c>
     </row>
     <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>31.10</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G143" s="4" t="inlineStr"/>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I143" s="6" t="inlineStr">
+      <c r="I143" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="J143" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K143" s="6" t="inlineStr">
+      <c r="K143" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -8194,53 +8203,53 @@
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>31.10</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G146" s="4" t="inlineStr"/>
-      <c r="H146" s="5" t="inlineStr">
+      <c r="G146" s="7" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
+      <c r="I146" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J146" s="5" t="inlineStr">
+      <c r="J146" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K146" s="6" t="inlineStr">
+      <c r="K146" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -8834,53 +8843,53 @@
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D158" s="7" t="inlineStr">
+      <c r="D158" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G158" s="7" t="inlineStr"/>
-      <c r="H158" s="8" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" s="5" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I158" s="9" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J158" s="8" t="inlineStr">
+      <c r="J158" s="5" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K158" s="9" t="inlineStr">
+      <c r="K158" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -9205,53 +9214,53 @@
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D165" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G165" s="4" t="inlineStr"/>
-      <c r="H165" s="5" t="inlineStr">
+      <c r="G165" s="7" t="inlineStr"/>
+      <c r="H165" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I165" s="6" t="inlineStr">
+      <c r="I165" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J165" s="5" t="inlineStr">
+      <c r="J165" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="K165" s="6" t="inlineStr">
+      <c r="K165" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
@@ -9682,53 +9691,53 @@
       </c>
     </row>
     <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="D174" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G174" s="4" t="inlineStr"/>
-      <c r="H174" s="5" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr"/>
+      <c r="H174" s="8" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="I174" s="6" t="inlineStr">
+      <c r="I174" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J174" s="5" t="inlineStr">
+      <c r="J174" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K174" s="6" t="inlineStr">
+      <c r="K174" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -9841,53 +9850,53 @@
       </c>
     </row>
     <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D177" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr"/>
-      <c r="H177" s="5" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I177" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J177" s="5" t="inlineStr">
+      <c r="J177" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K177" s="6" t="inlineStr">
+      <c r="K177" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -10000,159 +10009,159 @@
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D180" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr"/>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr"/>
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I180" s="6" t="inlineStr">
+      <c r="I180" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J180" s="5" t="inlineStr">
+      <c r="J180" s="8" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="K180" s="6" t="inlineStr">
+      <c r="K180" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D181" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr"/>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr"/>
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I181" s="6" t="inlineStr">
+      <c r="I181" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J181" s="5" t="inlineStr">
+      <c r="J181" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K181" s="6" t="inlineStr">
+      <c r="K181" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>14.11</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G182" s="4" t="inlineStr"/>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr"/>
+      <c r="H182" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I182" s="6" t="inlineStr">
+      <c r="I182" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J182" s="5" t="inlineStr">
+      <c r="J182" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="K182" s="6" t="inlineStr">
+      <c r="K182" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
@@ -10212,106 +10221,106 @@
       </c>
     </row>
     <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D184" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G184" s="4" t="inlineStr"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="G184" s="7" t="inlineStr"/>
+      <c r="H184" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I184" s="6" t="inlineStr">
+      <c r="I184" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J184" s="5" t="inlineStr">
+      <c r="J184" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K184" s="6" t="inlineStr">
+      <c r="K184" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D185" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F185" s="4" t="inlineStr">
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G185" s="4" t="inlineStr"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="G185" s="7" t="inlineStr"/>
+      <c r="H185" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I185" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J185" s="5" t="inlineStr">
+      <c r="J185" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="K185" s="6" t="inlineStr">
+      <c r="K185" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
@@ -10424,106 +10433,106 @@
       </c>
     </row>
     <row r="188" ht="15" customHeight="1">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="D188" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="inlineStr">
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G188" s="4" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr"/>
+      <c r="H188" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="I188" s="6" t="inlineStr">
+      <c r="I188" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J188" s="5" t="inlineStr">
+      <c r="J188" s="8" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="K188" s="6" t="inlineStr">
+      <c r="K188" s="9" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
+      <c r="A189" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
+      <c r="D189" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G189" s="4" t="inlineStr"/>
-      <c r="H189" s="5" t="inlineStr">
+      <c r="G189" s="7" t="inlineStr"/>
+      <c r="H189" s="8" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="I189" s="6" t="inlineStr">
+      <c r="I189" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J189" s="5" t="inlineStr">
+      <c r="J189" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K189" s="6" t="inlineStr">
+      <c r="K189" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -10583,106 +10592,106 @@
       </c>
     </row>
     <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D191" s="4" t="inlineStr">
+      <c r="D191" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G191" s="4" t="inlineStr"/>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="G191" s="7" t="inlineStr"/>
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="I191" s="6" t="inlineStr">
+      <c r="I191" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
-      <c r="J191" s="5" t="inlineStr">
+      <c r="J191" s="8" t="inlineStr">
         <is>
           <t>Киты 42/11</t>
         </is>
       </c>
-      <c r="K191" s="6" t="inlineStr">
+      <c r="K191" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="4" t="inlineStr">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>21.11</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="D192" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G192" s="4" t="inlineStr"/>
-      <c r="H192" s="5" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr"/>
+      <c r="H192" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I192" s="6" t="inlineStr">
+      <c r="I192" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J192" s="5" t="inlineStr">
+      <c r="J192" s="8" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="K192" s="6" t="inlineStr">
+      <c r="K192" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -10803,53 +10812,53 @@
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C195" s="7" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D195" s="7" t="inlineStr">
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E195" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr"/>
-      <c r="H195" s="8" t="inlineStr">
+      <c r="G195" s="4" t="inlineStr"/>
+      <c r="H195" s="5" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="I195" s="9" t="inlineStr">
+      <c r="I195" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J195" s="8" t="inlineStr">
+      <c r="J195" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K195" s="9" t="inlineStr">
+      <c r="K195" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -10970,53 +10979,53 @@
       </c>
     </row>
     <row r="198" ht="15" customHeight="1">
-      <c r="A198" s="4" t="inlineStr">
+      <c r="A198" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
+      <c r="D198" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G198" s="4" t="inlineStr"/>
-      <c r="H198" s="5" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr"/>
+      <c r="H198" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I198" s="6" t="inlineStr">
+      <c r="I198" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J198" s="5" t="inlineStr">
+      <c r="J198" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="K198" s="6" t="inlineStr">
+      <c r="K198" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
@@ -11190,106 +11199,106 @@
       </c>
     </row>
     <row r="202" ht="15" customHeight="1">
-      <c r="A202" s="7" t="inlineStr">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B202" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C202" s="7" t="inlineStr">
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D202" s="7" t="inlineStr">
+      <c r="D202" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E202" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F202" s="7" t="inlineStr">
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G202" s="7" t="inlineStr"/>
-      <c r="H202" s="8" t="inlineStr">
+      <c r="G202" s="4" t="inlineStr"/>
+      <c r="H202" s="5" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="I202" s="9" t="inlineStr">
+      <c r="I202" s="6" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
       </c>
-      <c r="J202" s="8" t="inlineStr">
+      <c r="J202" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K202" s="9" t="inlineStr">
+      <c r="K202" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="4" t="inlineStr">
+      <c r="A203" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D203" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr"/>
-      <c r="H203" s="5" t="inlineStr">
+      <c r="G203" s="7" t="inlineStr"/>
+      <c r="H203" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I203" s="6" t="inlineStr">
+      <c r="I203" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J203" s="5" t="inlineStr">
+      <c r="J203" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="K203" s="6" t="inlineStr">
+      <c r="K203" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
@@ -11516,106 +11525,106 @@
       </c>
     </row>
     <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="4" t="inlineStr">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="D208" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr"/>
-      <c r="H208" s="5" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr"/>
+      <c r="H208" s="8" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I208" s="6" t="inlineStr">
+      <c r="I208" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J208" s="5" t="inlineStr">
+      <c r="J208" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="K208" s="6" t="inlineStr">
+      <c r="K208" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="4" t="inlineStr">
+      <c r="A209" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="D209" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G209" s="4" t="inlineStr"/>
-      <c r="H209" s="5" t="inlineStr">
+      <c r="G209" s="7" t="inlineStr"/>
+      <c r="H209" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I209" s="6" t="inlineStr">
+      <c r="I209" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J209" s="5" t="inlineStr">
+      <c r="J209" s="8" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="K209" s="6" t="inlineStr">
+      <c r="K209" s="9" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
@@ -11732,159 +11741,159 @@
       </c>
     </row>
     <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C212" s="7" t="inlineStr">
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D212" s="7" t="inlineStr">
+      <c r="D212" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G212" s="7" t="inlineStr"/>
-      <c r="H212" s="8" t="inlineStr">
+      <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I212" s="9" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J212" s="8" t="inlineStr">
+      <c r="J212" s="5" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="K212" s="9" t="inlineStr">
+      <c r="K212" s="6" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1">
-      <c r="A213" s="4" t="inlineStr">
+      <c r="A213" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D213" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G213" s="4" t="inlineStr"/>
-      <c r="H213" s="5" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr"/>
+      <c r="H213" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="I213" s="6" t="inlineStr">
+      <c r="I213" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
-      <c r="J213" s="5" t="inlineStr">
+      <c r="J213" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K213" s="6" t="inlineStr">
+      <c r="K213" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="4" t="inlineStr">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D214" s="4" t="inlineStr">
+      <c r="D214" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G214" s="4" t="inlineStr"/>
-      <c r="H214" s="5" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr"/>
+      <c r="H214" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="I214" s="6" t="inlineStr">
+      <c r="I214" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
       </c>
-      <c r="J214" s="5" t="inlineStr">
+      <c r="J214" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K214" s="6" t="inlineStr">
+      <c r="K214" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -12111,53 +12120,53 @@
       </c>
     </row>
     <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
+      <c r="A219" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D219" s="4" t="inlineStr">
+      <c r="D219" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F219" s="4" t="inlineStr">
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G219" s="4" t="inlineStr"/>
-      <c r="H219" s="5" t="inlineStr">
+      <c r="G219" s="7" t="inlineStr"/>
+      <c r="H219" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="I219" s="6" t="inlineStr">
+      <c r="I219" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
-      <c r="J219" s="5" t="inlineStr">
+      <c r="J219" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="K219" s="6" t="inlineStr">
+      <c r="K219" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
@@ -12217,53 +12226,53 @@
       </c>
     </row>
     <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="7" t="inlineStr">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B221" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C221" s="7" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D221" s="7" t="inlineStr">
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G221" s="7" t="inlineStr"/>
-      <c r="H221" s="8" t="inlineStr">
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I221" s="9" t="inlineStr">
+      <c r="I221" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J221" s="8" t="inlineStr">
+      <c r="J221" s="5" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="K221" s="9" t="inlineStr">
+      <c r="K221" s="6" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
@@ -12384,53 +12393,53 @@
       </c>
     </row>
     <row r="224" ht="15" customHeight="1">
-      <c r="A224" s="4" t="inlineStr">
+      <c r="A224" s="7" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D224" s="4" t="inlineStr">
+      <c r="D224" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G224" s="4" t="inlineStr"/>
-      <c r="H224" s="5" t="inlineStr">
+      <c r="G224" s="7" t="inlineStr"/>
+      <c r="H224" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="I224" s="6" t="inlineStr">
+      <c r="I224" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
-      <c r="J224" s="5" t="inlineStr">
+      <c r="J224" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="K224" s="6" t="inlineStr">
+      <c r="K224" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
@@ -12490,53 +12499,53 @@
       </c>
     </row>
     <row r="226" ht="15" customHeight="1">
-      <c r="A226" s="4" t="inlineStr">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="inlineStr">
+      <c r="B226" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C226" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D226" s="4" t="inlineStr">
+      <c r="D226" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G226" s="4" t="inlineStr"/>
-      <c r="H226" s="5" t="inlineStr">
+      <c r="G226" s="7" t="inlineStr"/>
+      <c r="H226" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="I226" s="6" t="inlineStr">
+      <c r="I226" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J226" s="5" t="inlineStr">
+      <c r="J226" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="K226" s="6" t="inlineStr">
+      <c r="K226" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
@@ -12649,106 +12658,106 @@
       </c>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="4" t="inlineStr">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="D229" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F229" s="4" t="inlineStr">
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G229" s="4" t="inlineStr"/>
-      <c r="H229" s="5" t="inlineStr">
+      <c r="G229" s="7" t="inlineStr"/>
+      <c r="H229" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="I229" s="6" t="inlineStr">
+      <c r="I229" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
-      <c r="J229" s="5" t="inlineStr">
+      <c r="J229" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K229" s="6" t="inlineStr">
+      <c r="K229" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="4" t="inlineStr">
+      <c r="A230" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D230" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F230" s="4" t="inlineStr">
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G230" s="4" t="inlineStr"/>
-      <c r="H230" s="5" t="inlineStr">
+      <c r="G230" s="7" t="inlineStr"/>
+      <c r="H230" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I230" s="6" t="inlineStr">
+      <c r="I230" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J230" s="5" t="inlineStr">
+      <c r="J230" s="8" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="K230" s="6" t="inlineStr">
+      <c r="K230" s="9" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
@@ -12808,106 +12817,106 @@
       </c>
     </row>
     <row r="232" ht="15" customHeight="1">
-      <c r="A232" s="4" t="inlineStr">
+      <c r="A232" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D232" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F232" s="4" t="inlineStr">
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G232" s="4" t="inlineStr"/>
-      <c r="H232" s="5" t="inlineStr">
+      <c r="G232" s="7" t="inlineStr"/>
+      <c r="H232" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="I232" s="6" t="inlineStr">
+      <c r="I232" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
       </c>
-      <c r="J232" s="5" t="inlineStr">
+      <c r="J232" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K232" s="6" t="inlineStr">
+      <c r="K232" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
+      <c r="A233" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C233" s="7" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D233" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F233" s="4" t="inlineStr">
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G233" s="4" t="inlineStr"/>
-      <c r="H233" s="5" t="inlineStr">
+      <c r="G233" s="7" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="I233" s="6" t="inlineStr">
+      <c r="I233" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
-      <c r="J233" s="5" t="inlineStr">
+      <c r="J233" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K233" s="6" t="inlineStr">
+      <c r="K233" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -12967,106 +12976,106 @@
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="4" t="inlineStr">
+      <c r="A235" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr">
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C235" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="D235" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #2</t>
         </is>
       </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F235" s="4" t="inlineStr">
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G235" s="4" t="inlineStr"/>
-      <c r="H235" s="5" t="inlineStr">
+      <c r="G235" s="7" t="inlineStr"/>
+      <c r="H235" s="8" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="I235" s="6" t="inlineStr">
+      <c r="I235" s="9" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
-      <c r="J235" s="5" t="inlineStr">
+      <c r="J235" s="8" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K235" s="6" t="inlineStr">
+      <c r="K235" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="4" t="inlineStr">
+      <c r="A236" s="7" t="inlineStr">
         <is>
           <t>05.12</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr">
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="D236" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F236" s="4" t="inlineStr">
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G236" s="4" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="G236" s="7" t="inlineStr"/>
+      <c r="H236" s="8" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="I236" s="6" t="inlineStr">
+      <c r="I236" s="9" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
       </c>
-      <c r="J236" s="5" t="inlineStr">
+      <c r="J236" s="8" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K236" s="6" t="inlineStr">
+      <c r="K236" s="9" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -13126,106 +13135,106 @@
       </c>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="A238" s="7" t="inlineStr">
+      <c r="A238" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C238" s="7" t="inlineStr">
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D238" s="7" t="inlineStr">
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E238" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F238" s="7" t="inlineStr">
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G238" s="7" t="inlineStr"/>
-      <c r="H238" s="8" t="inlineStr">
+      <c r="G238" s="4" t="inlineStr"/>
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="I238" s="9" t="inlineStr">
+      <c r="I238" s="6" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
       </c>
-      <c r="J238" s="8" t="inlineStr">
+      <c r="J238" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K238" s="9" t="inlineStr">
+      <c r="K238" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="7" t="inlineStr">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B239" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C239" s="7" t="inlineStr">
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D239" s="7" t="inlineStr">
+      <c r="D239" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E239" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G239" s="7" t="inlineStr"/>
-      <c r="H239" s="8" t="inlineStr">
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="I239" s="9" t="inlineStr">
+      <c r="I239" s="6" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
-      <c r="J239" s="8" t="inlineStr">
+      <c r="J239" s="5" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="K239" s="9" t="inlineStr">
+      <c r="K239" s="6" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
@@ -13399,106 +13408,106 @@
       </c>
     </row>
     <row r="243" ht="15" customHeight="1">
-      <c r="A243" s="7" t="inlineStr">
+      <c r="A243" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B243" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C243" s="7" t="inlineStr">
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D243" s="7" t="inlineStr">
+      <c r="D243" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E243" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F243" s="7" t="inlineStr">
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G243" s="7" t="inlineStr"/>
-      <c r="H243" s="8" t="inlineStr">
+      <c r="G243" s="4" t="inlineStr"/>
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="I243" s="9" t="inlineStr">
+      <c r="I243" s="6" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
       </c>
-      <c r="J243" s="8" t="inlineStr">
+      <c r="J243" s="5" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K243" s="9" t="inlineStr">
+      <c r="K243" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1">
-      <c r="A244" s="7" t="inlineStr">
+      <c r="A244" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B244" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C244" s="7" t="inlineStr">
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D244" s="7" t="inlineStr">
+      <c r="D244" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E244" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F244" s="7" t="inlineStr">
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G244" s="7" t="inlineStr"/>
-      <c r="H244" s="8" t="inlineStr">
+      <c r="G244" s="4" t="inlineStr"/>
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>школа 76</t>
         </is>
       </c>
-      <c r="I244" s="9" t="inlineStr">
+      <c r="I244" s="6" t="inlineStr">
         <is>
           <t>Глинин</t>
         </is>
       </c>
-      <c r="J244" s="8" t="inlineStr">
+      <c r="J244" s="5" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="K244" s="9" t="inlineStr">
+      <c r="K244" s="6" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
@@ -13558,53 +13567,53 @@
       </c>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="A246" s="7" t="inlineStr">
+      <c r="A246" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B246" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C246" s="7" t="inlineStr">
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D246" s="7" t="inlineStr">
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E246" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F246" s="7" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G246" s="7" t="inlineStr"/>
-      <c r="H246" s="8" t="inlineStr">
+      <c r="G246" s="4" t="inlineStr"/>
+      <c r="H246" s="5" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="I246" s="9" t="inlineStr">
+      <c r="I246" s="6" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
       </c>
-      <c r="J246" s="8" t="inlineStr">
+      <c r="J246" s="5" t="inlineStr">
         <is>
           <t>Профики 2</t>
         </is>
       </c>
-      <c r="K246" s="9" t="inlineStr">
+      <c r="K246" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -13721,53 +13730,53 @@
       </c>
     </row>
     <row r="249" ht="15" customHeight="1">
-      <c r="A249" s="7" t="inlineStr">
+      <c r="A249" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B249" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C249" s="7" t="inlineStr">
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D249" s="7" t="inlineStr">
+      <c r="D249" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E249" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F249" s="7" t="inlineStr">
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G249" s="7" t="inlineStr"/>
-      <c r="H249" s="8" t="inlineStr">
+      <c r="G249" s="4" t="inlineStr"/>
+      <c r="H249" s="5" t="inlineStr">
         <is>
           <t>ЯнгФорс</t>
         </is>
       </c>
-      <c r="I249" s="9" t="inlineStr">
+      <c r="I249" s="6" t="inlineStr">
         <is>
           <t>Сусляев</t>
         </is>
       </c>
-      <c r="J249" s="8" t="inlineStr">
+      <c r="J249" s="5" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="K249" s="9" t="inlineStr">
+      <c r="K249" s="6" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
@@ -13884,53 +13893,53 @@
       </c>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="4" t="inlineStr">
+      <c r="A252" s="7" t="inlineStr">
         <is>
           <t>19.12</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr">
+      <c r="B252" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D252" s="4" t="inlineStr">
+      <c r="D252" s="7" t="inlineStr">
         <is>
           <t>Поле 5*5 #3</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F252" s="4" t="inlineStr">
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G252" s="4" t="inlineStr"/>
-      <c r="H252" s="5" t="inlineStr">
+      <c r="G252" s="7" t="inlineStr"/>
+      <c r="H252" s="8" t="inlineStr">
         <is>
           <t>Барселона</t>
         </is>
       </c>
-      <c r="I252" s="6" t="inlineStr">
+      <c r="I252" s="9" t="inlineStr">
         <is>
           <t>Ботов</t>
         </is>
       </c>
-      <c r="J252" s="5" t="inlineStr">
+      <c r="J252" s="8" t="inlineStr">
         <is>
           <t>Молот (153/157)</t>
         </is>
       </c>
-      <c r="K252" s="6" t="inlineStr">
+      <c r="K252" s="9" t="inlineStr">
         <is>
           <t>Вукалов</t>
         </is>
@@ -14096,159 +14105,159 @@
       </c>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="7" t="inlineStr">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B256" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C256" s="7" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D256" s="7" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E256" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F256" s="7" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G256" s="7" t="inlineStr"/>
-      <c r="H256" s="8" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr"/>
+      <c r="H256" s="5" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I256" s="9" t="inlineStr">
+      <c r="I256" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J256" s="8" t="inlineStr">
+      <c r="J256" s="5" t="inlineStr">
         <is>
           <t>Крепыши 3</t>
         </is>
       </c>
-      <c r="K256" s="9" t="inlineStr">
+      <c r="K256" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="7" t="inlineStr">
+      <c r="A257" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B257" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C257" s="7" t="inlineStr">
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D257" s="7" t="inlineStr">
+      <c r="D257" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E257" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F257" s="7" t="inlineStr">
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G257" s="7" t="inlineStr"/>
-      <c r="H257" s="8" t="inlineStr">
+      <c r="G257" s="4" t="inlineStr"/>
+      <c r="H257" s="5" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="I257" s="9" t="inlineStr">
+      <c r="I257" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J257" s="8" t="inlineStr">
+      <c r="J257" s="5" t="inlineStr">
         <is>
           <t>Крепыши</t>
         </is>
       </c>
-      <c r="K257" s="9" t="inlineStr">
+      <c r="K257" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1">
-      <c r="A258" s="7" t="inlineStr">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B258" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C258" s="7" t="inlineStr">
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D258" s="7" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E258" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F258" s="7" t="inlineStr">
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G258" s="7" t="inlineStr"/>
-      <c r="H258" s="8" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr"/>
+      <c r="H258" s="5" t="inlineStr">
         <is>
           <t>Крепыши 2</t>
         </is>
       </c>
-      <c r="I258" s="9" t="inlineStr">
+      <c r="I258" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J258" s="8" t="inlineStr">
+      <c r="J258" s="5" t="inlineStr">
         <is>
           <t>Спутник</t>
         </is>
       </c>
-      <c r="K258" s="9" t="inlineStr">
+      <c r="K258" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -14335,42 +14344,42 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Сводка спортдиректора — 2×7×7 везде, 60 мин, без параллелей</t>
+          <t>Сводка спортдиректора — ТОЛЬКО 19 ДАТ (без января) • 2020 как 4×4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Запланировано: 255</t>
+          <t>Запланировано: 255 / 299 (7×7:45 5×5:176 4×4:78)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Не влезло (нужны доп. даты): 44</t>
+          <t>Не влезло (нужны доп. даты/январь): 44 (7×7:19 5×5:13 4×4:12)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Конфликтов (реальных параллелей): 0</t>
+          <t>Конфликтов (реальных параллелей): 0 ✓</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Слотов всего: 394 (136×7×7 +177×5×5 +81×4×4) — последовательных тайм-слотов 68</t>
+          <t>Слотов всего ТОЛЬКО эти 19 дат: 394 (136×7×7 +177×5×5 +81×4×4) — последовательных тайм-слотов 68 — январь пока не известен</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Регламент: 2×25+5 перерыв между таймами +5 между матчами =60 мин; 2020: 2×20+5+15=60 мин</t>
+          <t>Регламент: 2×25+5 перерыв между таймами +5 между матчами =60 мин; 2020-2021: 2×20+5 перерыв+15 между матчами =60 мин (формат 4×4 отмечено)</t>
         </is>
       </c>
     </row>
@@ -14924,4 +14933,3697 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — ТОЛЬКО формат 4×4 — только эти 19 дат (январь — продолжение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Регламент: 2×20+5 перерыв+15 между матчами =60 мин/игра — на поле 4×4 (может играть на 5×5 — жёлтым) — без параллелей тренеров</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Формат</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Лига</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Хозяева</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Гости</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Тренер</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>27.08</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>04.10</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>25.10</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>25.10</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>25.10</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>31.10</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>31.10</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>21.11</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>28.11</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>05.12</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>школа 76</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Глинин</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>12.12</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>ЯнгФорс</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Сусляев</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Барселона</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Ботов</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Молот (153/157)</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>Вукалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>26.12</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>4*4</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Не влезло 2020 на эти 19 дат — 12 матчей — уйдут в январь:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>школа 76 — Крепыши 2 (Глинин/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>Молот (153/157) — Крепыши (Вукалов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>ЯнгФорс — Крепыши 2 (Сусляев/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши 2 — Барселона (Анисимов/Ботов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши 2 — Молот (153/157) (Анисимов/Вукалов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши 3 — школа 76 (Анисимов/Глинин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши — школа 76 (Анисимов/Глинин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши 3 — ЯнгФорс (Анисимов/Сусляев)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>Крепыши — ЯнгФорс (Анисимов/Сусляев)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>Барселона — Крепыши 3 (Ботов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>Молот (153/157) — Крепыши 3 (Вукалов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>Барселона — Крепыши (Ботов/Анисимов)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K70"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>